--- a/tables/supplement_table_mouse_1.xlsx
+++ b/tables/supplement_table_mouse_1.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 - Per-source contribution" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 - Full ledger" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -81,6 +82,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6049,4 +6053,397 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>accession</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>version_snapshot</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>derived_path_in_repo</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>PanSci</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Zhang et al. Nature 2024</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>GSE247719</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE247719</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>data/pansci/ (gitignored, see data_manifest/README.md §2.1)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>sci-RNA-seq3 mouse pan-organ aging atlas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>EasySci brain</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Sziraki et al. Nature Aging 2023</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>GSE212606</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE212606</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>data/pansci/brain/ (gitignored)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>EasySci, brain-optimised</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TMS (Tabula Muris Senis)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Schaum et al. Nature 2020</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>figshare:8273102</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://figshare.com/articles/dataset/8273102</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>data/tms/per_organ/ (gitignored)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Smart-seq2 FACS + 10x Chromium Droplet, 23 organs × 6 ages</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MCA2 (Mouse Cell Atlas 2.0)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Han et al. Cell 2022</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>GSE153562</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE153562</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>data/mca2/ (gitignored)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Microwell-seq, fills aged-organ gaps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Hammond microglia</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Olah et al. Nat Commun 2020</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>GSE179358</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE179358</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>data/microglia_aging/ (gitignored)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>10x microglia FACS-sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Whole-body Array-seq mouse</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Clevenger et al. Cell 2026</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>GSE248904</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE248904</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>data/st/ + data/st/per_organ/ (gitignored)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Spatial reference for CMap projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>CMap (single-cell → spatial mapping)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>scripts/preprocess_new_sc.py + scripts/process_remaining_gaps.py</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>models/cmap_output/{organ}/{sample}.h5ad (gitignored)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Projects each source single-cell sample onto Clevenger 2026 spatial reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>gsMap</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Liu et al. Nature Methods 2024</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>GitHub: JianYang-Lab/gsMap</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/JianYang-Lab/gsMap</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>v1.x</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>models/gsmap_age_output/{sample}/ (gitignored)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Spatial S-LDSC per (sample × annotation) Cauchy combination</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Derived provenance CSV</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>This work</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>results/age_sample_provenance_per_source.csv</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Rebuilt by scripts/build_age_provenance_per_source.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>